--- a/www/terminologies/CodeSystem-terminologie-sms.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-07</t>
+    <t>2026-08</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T10:00:00+00:00</t>
+    <t>2026-08-04T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>72342</t>
+    <t>72536</t>
   </si>
   <si>
     <t>Code</t>

--- a/www/terminologies/CodeSystem-terminologie-sms.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-08</t>
+    <t>2026-09</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T10:00:00+00:00</t>
+    <t>2026-09-04T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>72536</t>
+    <t>72708</t>
   </si>
   <si>
     <t>Code</t>
